--- a/7rmartsupermarket/src/test/resources/TestData.xlsx
+++ b/7rmartsupermarket/src/test/resources/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="2"/>
+    <workbookView windowWidth="13128" windowHeight="3792" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>username</t>
   </si>
@@ -83,12 +83,6 @@
   </si>
   <si>
     <t>Trivandrum</t>
-  </si>
-  <si>
-    <t>"10:00:00"</t>
-  </si>
-  <si>
-    <t>"1000"</t>
   </si>
   <si>
     <t>enterthenews</t>
@@ -1194,11 +1188,11 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
+      <c r="D2" s="2">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="E2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -1218,12 +1212,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1256,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1285,12 +1279,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/7rmartsupermarket/src/test/resources/TestData.xlsx
+++ b/7rmartsupermarket/src/test/resources/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13128" windowHeight="3792" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="8400" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,8 @@
     <sheet name="newspage" sheetId="4" r:id="rId4"/>
     <sheet name="managefootertextpage" sheetId="5" r:id="rId5"/>
     <sheet name="managecategorypage" sheetId="6" r:id="rId6"/>
+    <sheet name="managedeliveryboypage" sheetId="7" r:id="rId7"/>
+    <sheet name="managelocationpage" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>username</t>
   </si>
@@ -98,6 +100,30 @@
   </si>
   <si>
     <t>Snacks</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Trivandrm</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>deliverycharge</t>
+  </si>
+  <si>
+    <t>Cambridge</t>
+  </si>
+  <si>
+    <t>university</t>
   </si>
 </sst>
 </file>
@@ -1291,4 +1317,101 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="25.7" customWidth="1"/>
+    <col min="3" max="3" width="11.6"/>
+    <col min="6" max="6" width="11.6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="rahulkrishnanpd@gmail.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="13.6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>